--- a/y11619/forecast_1.xlsx
+++ b/y11619/forecast_1.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -478,7 +478,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-26 19:50:27</t>
+          <t>2026-05-28 03:50:55</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-26 至 2026-08-26</t>
+          <t>2026-05-28 至 2026-08-28</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>预计过期积分</t>
+          <t>预计过期积分(正常)</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -560,192 +560,173 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>预计退款返积分</t>
+          <t>跨月过期积分(不计入负债)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>预计兑换消耗积分</t>
+          <t>预计退款返积分</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>28000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>预计兑换券成本(元)</t>
+          <t>预计兑换消耗积分</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8000</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总预计负债(元)</t>
+          <t>预计兑换券成本(元)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8150</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>总预计负债(元)</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>8150</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>积分折算比例(元/积分)</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B18" t="n">
         <v>0.01</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>负债构成分析</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>项目</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>金额(元)</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>占比</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>积分过期负债</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>150</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1.8%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>退款返积分负债</t>
+          <t>积分过期负债(正常)</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.8%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>退款返积分负债</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>兑换券成本</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="B24" t="n">
         <v>8000</v>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>98.2%</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>跨月过期负债(不计入合计)</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>500</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>风险提示</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>级别</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>提示信息</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>来源参考</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>cross_month_expiry</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>会员 M001 的积分 3000 在预测期外跨月过期</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>交易ID=1, 源行号=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>cross_month_expiry</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>会员 M001 的积分 2000 在预测期外跨月过期</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>交易ID=2, 源行号=2</t>
         </is>
       </c>
     </row>
@@ -762,12 +743,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>会员 M002 的积分 3000 在预测期外跨月过期</t>
+          <t>会员 M001 的积分 3000 在预测期外跨月过期，不计入本期正常负债</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>交易ID=3, 源行号=3</t>
+          <t>交易ID=1, 源行号=1</t>
         </is>
       </c>
     </row>
@@ -784,12 +765,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>会员 M002 的积分 2000 在预测期外跨月过期</t>
+          <t>会员 M001 的积分 2000 在预测期外跨月过期，不计入本期正常负债</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>交易ID=4, 源行号=4</t>
+          <t>交易ID=2, 源行号=2</t>
         </is>
       </c>
     </row>
@@ -806,12 +787,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>会员 M003 的积分 3000 在预测期外跨月过期</t>
+          <t>会员 M002 的积分 3000 在预测期外跨月过期，不计入本期正常负债</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>交易ID=6, 源行号=6</t>
+          <t>交易ID=3, 源行号=3</t>
         </is>
       </c>
     </row>
@@ -828,12 +809,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>会员 M003 的积分 2000 在预测期外跨月过期</t>
+          <t>会员 M002 的积分 2000 在预测期外跨月过期，不计入本期正常负债</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>交易ID=7, 源行号=7</t>
+          <t>交易ID=4, 源行号=4</t>
         </is>
       </c>
     </row>
@@ -850,12 +831,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>会员 M004 的积分 3000 在预测期外跨月过期</t>
+          <t>会员 M003 的积分 3000 在预测期外跨月过期，不计入本期正常负债</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>交易ID=8, 源行号=8</t>
+          <t>交易ID=6, 源行号=6</t>
         </is>
       </c>
     </row>
@@ -872,12 +853,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>会员 M004 的积分 2000 在预测期外跨月过期</t>
+          <t>会员 M003 的积分 2000 在预测期外跨月过期，不计入本期正常负债</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>交易ID=9, 源行号=9</t>
+          <t>交易ID=7, 源行号=7</t>
         </is>
       </c>
     </row>
@@ -894,12 +875,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>会员 M005 的积分 3000 在预测期外跨月过期</t>
+          <t>会员 M004 的积分 3000 在预测期外跨月过期，不计入本期正常负债</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>交易ID=10, 源行号=10</t>
+          <t>交易ID=8, 源行号=8</t>
         </is>
       </c>
     </row>
@@ -916,12 +897,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>会员 M005 的积分 2000 在预测期外跨月过期</t>
+          <t>会员 M004 的积分 2000 在预测期外跨月过期，不计入本期正常负债</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>交易ID=11, 源行号=11</t>
+          <t>交易ID=9, 源行号=9</t>
         </is>
       </c>
     </row>
@@ -938,12 +919,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>会员 M006 的积分 3000 在预测期外跨月过期</t>
+          <t>会员 M005 的积分 3000 在预测期外跨月过期，不计入本期正常负债</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>交易ID=13, 源行号=13</t>
+          <t>交易ID=10, 源行号=10</t>
         </is>
       </c>
     </row>
@@ -960,12 +941,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>会员 M006 的积分 2000 在预测期外跨月过期</t>
+          <t>会员 M005 的积分 2000 在预测期外跨月过期，不计入本期正常负债</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>交易ID=14, 源行号=14</t>
+          <t>交易ID=11, 源行号=11</t>
         </is>
       </c>
     </row>
@@ -982,12 +963,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>会员 M007 的积分 3000 在预测期外跨月过期</t>
+          <t>会员 M006 的积分 3000 在预测期外跨月过期，不计入本期正常负债</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>交易ID=15, 源行号=15</t>
+          <t>交易ID=13, 源行号=13</t>
         </is>
       </c>
     </row>
@@ -1004,12 +985,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>会员 M007 的积分 2000 在预测期外跨月过期</t>
+          <t>会员 M006 的积分 2000 在预测期外跨月过期，不计入本期正常负债</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>交易ID=16, 源行号=16</t>
+          <t>交易ID=14, 源行号=14</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1007,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>会员 M008 的积分 3000 在预测期外跨月过期</t>
+          <t>会员 M007 的积分 3000 在预测期外跨月过期，不计入本期正常负债</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>交易ID=17, 源行号=17</t>
+          <t>交易ID=15, 源行号=15</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1029,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>会员 M008 的积分 2000 在预测期外跨月过期</t>
+          <t>会员 M007 的积分 2000 在预测期外跨月过期，不计入本期正常负债</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>交易ID=18, 源行号=18</t>
+          <t>交易ID=16, 源行号=16</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1051,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>会员 M009 的积分 3000 在预测期外跨月过期</t>
+          <t>会员 M008 的积分 3000 在预测期外跨月过期，不计入本期正常负债</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>交易ID=20, 源行号=20</t>
+          <t>交易ID=17, 源行号=17</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1073,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>会员 M009 的积分 2000 在预测期外跨月过期</t>
+          <t>会员 M008 的积分 2000 在预测期外跨月过期，不计入本期正常负债</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>交易ID=21, 源行号=21</t>
+          <t>交易ID=18, 源行号=18</t>
         </is>
       </c>
     </row>
@@ -1114,12 +1095,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>会员 M010 的积分 3000 在预测期外跨月过期</t>
+          <t>会员 M009 的积分 3000 在预测期外跨月过期，不计入本期正常负债</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>交易ID=22, 源行号=22</t>
+          <t>交易ID=20, 源行号=20</t>
         </is>
       </c>
     </row>
@@ -1136,172 +1117,178 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>会员 M010 的积分 2000 在预测期外跨月过期</t>
+          <t>会员 M009 的积分 2000 在预测期外跨月过期，不计入本期正常负债</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t>交易ID=21, 源行号=21</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>cross_month_expiry</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>会员 M010 的积分 3000 在预测期外跨月过期，不计入本期正常负债</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>交易ID=22, 源行号=22</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>cross_month_expiry</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>会员 M010 的积分 2000 在预测期外跨月过期，不计入本期正常负债</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
           <t>交易ID=23, 源行号=23</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>修正记录</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>修正时间</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>字段</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>原值</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D51" s="4" t="inlineStr">
         <is>
           <t>新值</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
+      <c r="E51" s="4" t="inlineStr">
         <is>
           <t>修正原因</t>
         </is>
       </c>
-      <c r="F49" s="4" t="inlineStr">
+      <c r="F51" s="4" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2026-05-26 19:50:27</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-05-28 03:50:55</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
         <is>
           <t>expected_expired_points</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>23000</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
         <is>
           <t>15000</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>根据历史数据调整过期预估，6月过期积分约1.5万</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>财务-小红</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>预测曲线数据</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>累计负债(元)</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>累计过期积分</t>
         </is>
       </c>
-      <c r="D53" s="4" t="inlineStr">
+      <c r="D55" s="4" t="inlineStr">
         <is>
           <t>累计兑换积分</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
+      <c r="E55" s="4" t="inlineStr">
         <is>
           <t>累计退款积分</t>
         </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>2666.666666666667</v>
-      </c>
-      <c r="C54" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" t="n">
-        <v>9333</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>5247.311827956989</v>
-      </c>
-      <c r="C55" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" t="n">
-        <v>18365</v>
-      </c>
-      <c r="E55" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>8143.978494623656</v>
+        <v>2666.666666666667</v>
       </c>
       <c r="C56" t="n">
-        <v>23000</v>
+        <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>27698</v>
+        <v>9333</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
@@ -1310,19 +1297,57 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B57" t="n">
+        <v>5247.311827956989</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" t="n">
+        <v>18365</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>8143.978494623656</v>
+      </c>
+      <c r="C58" t="n">
+        <v>23000</v>
+      </c>
+      <c r="D58" t="n">
+        <v>27698</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
         <v>8230</v>
       </c>
-      <c r="C57" t="n">
+      <c r="C59" t="n">
         <v>23000</v>
       </c>
-      <c r="D57" t="n">
+      <c r="D59" t="n">
         <v>28000</v>
       </c>
-      <c r="E57" t="n">
+      <c r="E59" t="n">
         <v>0</v>
       </c>
     </row>
